--- a/artfynd/A 19007-2022 artfynd.xlsx
+++ b/artfynd/A 19007-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19007-2022 artfynd.xlsx
+++ b/artfynd/A 19007-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103260768</v>
+        <v>103260753</v>
       </c>
       <c r="B2" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697712.2072892517</v>
+        <v>697646</v>
       </c>
       <c r="R2" t="n">
-        <v>7155155.135429531</v>
+        <v>7155139</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +754,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103261081</v>
+        <v>103261027</v>
       </c>
       <c r="B3" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -846,14 +826,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Degermyrbacken, Vb</t>
+          <t>Degermyrbacken, Ekorrsele, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697815.5072216147</v>
+        <v>697797</v>
       </c>
       <c r="R3" t="n">
-        <v>7155145.398385679</v>
+        <v>7155172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,19 +863,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103260735</v>
+        <v>103260768</v>
       </c>
       <c r="B4" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,26 +904,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -974,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697645.6663341868</v>
+        <v>697712</v>
       </c>
       <c r="R4" t="n">
-        <v>7155139.13725552</v>
+        <v>7155155</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,19 +972,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,15 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103261027</v>
+        <v>103261081</v>
       </c>
       <c r="B5" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1094,14 +1044,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Degermyrbacken, Ekorrsele, Vb</t>
+          <t>Degermyrbacken, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697797.2969363381</v>
+        <v>697816</v>
       </c>
       <c r="R5" t="n">
-        <v>7155172.338980326</v>
+        <v>7155146</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,19 +1081,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,19 +1111,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103260808</v>
+        <v>103260755</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1206,7 +1141,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1222,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697799.5929893174</v>
+        <v>697646</v>
       </c>
       <c r="R6" t="n">
-        <v>7155217.051073908</v>
+        <v>7155139</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,19 +1190,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,15 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103261053</v>
+        <v>103260781</v>
       </c>
       <c r="B7" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,26 +1231,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1346,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697797.2969363381</v>
+        <v>697672</v>
       </c>
       <c r="R7" t="n">
-        <v>7155172.338980326</v>
+        <v>7155103</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,19 +1299,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,19 +1329,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103261091</v>
+        <v>103260801</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1466,14 +1371,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Degermyrbacken, Vb</t>
+          <t>Degermyrbacken, Ekorrsele, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697815.5072216147</v>
+        <v>697736</v>
       </c>
       <c r="R8" t="n">
-        <v>7155145.398385679</v>
+        <v>7155072</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1503,19 +1408,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1543,19 +1438,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103260781</v>
+        <v>103260808</v>
       </c>
       <c r="B9" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1578,7 +1468,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1594,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697672.2272454798</v>
+        <v>697799</v>
       </c>
       <c r="R9" t="n">
-        <v>7155103.651429688</v>
+        <v>7155217</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1627,19 +1517,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1670,16 +1550,11 @@
         <v>103261020</v>
       </c>
       <c r="B10" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1718,10 +1593,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697797.2969363381</v>
+        <v>697797</v>
       </c>
       <c r="R10" t="n">
-        <v>7155172.338980326</v>
+        <v>7155172</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1751,19 +1626,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1791,19 +1656,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103260801</v>
+        <v>103261091</v>
       </c>
       <c r="B11" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1838,14 +1698,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Degermyrbacken, Ekorrsele, Vb</t>
+          <t>Degermyrbacken, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697735.4012438387</v>
+        <v>697816</v>
       </c>
       <c r="R11" t="n">
-        <v>7155071.406128489</v>
+        <v>7155146</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1875,19 +1735,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1915,42 +1765,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103260755</v>
+        <v>103261053</v>
       </c>
       <c r="B12" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1966,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697645.6663341868</v>
+        <v>697797</v>
       </c>
       <c r="R12" t="n">
-        <v>7155139.13725552</v>
+        <v>7155172</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1999,19 +1844,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2036,130 +1871,6 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>103260753</v>
-      </c>
-      <c r="B13" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Hydnellum aurantiacum</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Degermyrbacken, Ekorrsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>697645.6663341868</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7155139.13725552</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Ulf Hallin</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Ulf Hallin</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19007-2022 artfynd.xlsx
+++ b/artfynd/A 19007-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103260753</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103261027</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103260768</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103261081</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103260755</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103260781</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,6 +1470,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103260801</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1544,6 +1584,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103260808</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1653,6 +1698,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103261020</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103261091</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1871,8 +1926,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103261053</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>